--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="188">
   <si>
     <t>Honda City 1.5 V MT Exclusive</t>
   </si>
@@ -912,7 +912,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2120,6 +2120,1118 @@
         <v>69</v>
       </c>
       <c r="B151" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B245" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B246" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B247" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B248" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B249" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B250" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B251" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B252" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B253" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B254" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B255" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B256" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B257" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B258" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B259" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B260" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B261" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B262" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B263" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B264" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B265" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B266" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B267" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B268" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B269" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B270" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B271" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B272" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B273" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B274" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B275" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B276" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B277" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B278" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="B279" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B280" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B281" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B282" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B283" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B284" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B285" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B286" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B287" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B288" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B289" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B290" t="s" s="0">
         <v>186</v>
       </c>
     </row>
@@ -2130,7 +3242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2218,6 +3330,171 @@
         <v>141</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497760\Ideaprojects\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12C0AC9-9A3D-49DB-9861-5AE55ECAA867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412D0D53-2C7B-444A-A8FB-D529F36BD621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BAA70594-9921-46EE-9B36-55EF6409868E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CarDetails" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,8 +39,74 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>Honda City 1.5 S MT</t>
+  </si>
+  <si>
+    <t>Rs. 4.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT Exclusive</t>
+  </si>
+  <si>
+    <t>Rs. 4.55 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna</t>
+  </si>
+  <si>
+    <t>Rs. 3.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City SV MT</t>
+  </si>
+  <si>
+    <t>Rs. 5.15 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.1L</t>
+  </si>
+  <si>
+    <t>Rs. 3.65 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.70 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 4.84 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT</t>
+  </si>
+  <si>
+    <t>Rs. 6.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX MT</t>
+  </si>
+  <si>
+    <t>Rs. 9.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.90 Lakh</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,4 +477,102 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="CarDetails" r:id="rId5" sheetId="2"/>
     <sheet name="Under3LakhCars" r:id="rId6" sheetId="3"/>
+    <sheet name="HondaBikeDetails" r:id="rId7" sheetId="4"/>
+    <sheet name="BikesUnder4Lakhs" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="224">
   <si>
     <t>Honda City 1.5 V MT Exclusive</t>
   </si>
@@ -585,6 +587,114 @@
   </si>
   <si>
     <t>Car Name</t>
+  </si>
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Expected Launch</t>
+  </si>
+  <si>
+    <t>Honda ADV 160</t>
+  </si>
+  <si>
+    <t>Rs. 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Dec 2026</t>
+  </si>
+  <si>
+    <t>Honda Shine Electric</t>
+  </si>
+  <si>
+    <t>Rs. 1.30 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Jan 2028</t>
+  </si>
+  <si>
+    <t>Honda CBR500R</t>
+  </si>
+  <si>
+    <t>Expected Launch : Unrevealed</t>
+  </si>
+  <si>
+    <t>Honda Forza 350</t>
+  </si>
+  <si>
+    <t>Honda Rebel 1100</t>
+  </si>
+  <si>
+    <t>Rs. 12.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB500F</t>
+  </si>
+  <si>
+    <t>Rs. 5.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CBR150R</t>
+  </si>
+  <si>
+    <t>Rs. 1.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 300</t>
+  </si>
+  <si>
+    <t>Rs. 2.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda PCX160</t>
+  </si>
+  <si>
+    <t>Rs. 1.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Motocompacto</t>
+  </si>
+  <si>
+    <t>Price To Be Announced</t>
+  </si>
+  <si>
+    <t>Honda CRF300L</t>
+  </si>
+  <si>
+    <t>Rs. 3.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB350 Cruiser</t>
+  </si>
+  <si>
+    <t>Honda Activa 7G</t>
+  </si>
+  <si>
+    <t>Rs. 79,000</t>
+  </si>
+  <si>
+    <t>Honda CB1000R</t>
+  </si>
+  <si>
+    <t>Rs. 14.46 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB1000GT</t>
+  </si>
+  <si>
+    <t>Honda WN7</t>
+  </si>
+  <si>
+    <t>Honda SH125i</t>
+  </si>
+  <si>
+    <t>Honda CL500 Scrambler</t>
+  </si>
+  <si>
+    <t>Rs. 6.00 Lakh</t>
   </si>
 </sst>
 </file>
@@ -3242,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3605,1514 @@
         <v>141</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="224">
   <si>
     <t>Honda City 1.5 V MT Exclusive</t>
   </si>
@@ -3692,7 +3692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4297,6 +4297,204 @@
         <v>223</v>
       </c>
       <c r="C55" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C73" t="s" s="0">
         <v>198</v>
       </c>
     </row>
@@ -4307,7 +4505,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5113,6 +5311,402 @@
         <v>198</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -3,22 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497760\Ideaprojects\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412D0D53-2C7B-444A-A8FB-D529F36BD621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E008CE4-57D5-4C0C-A354-35351A46C240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BAA70594-9921-46EE-9B36-55EF6409868E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="CarDetails" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,74 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>Honda City 1.5 S MT</t>
-  </si>
-  <si>
-    <t>Rs. 4.60 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 V MT Exclusive</t>
-  </si>
-  <si>
-    <t>Rs. 4.55 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Magna</t>
-  </si>
-  <si>
-    <t>Rs. 3.20 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City SV MT</t>
-  </si>
-  <si>
-    <t>Rs. 5.15 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Sportz 1.1L</t>
-  </si>
-  <si>
-    <t>Rs. 3.65 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 4.70 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.25 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC CVT VX</t>
-  </si>
-  <si>
-    <t>Rs. 4.84 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City V MT</t>
-  </si>
-  <si>
-    <t>Rs. 6.70 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City ZX MT</t>
-  </si>
-  <si>
-    <t>Rs. 9.25 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC V</t>
-  </si>
-  <si>
-    <t>Rs. 6.90 Lakh</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -477,102 +410,4 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="224">
   <si>
     <t>Honda City 1.5 V MT Exclusive</t>
   </si>
@@ -3692,7 +3692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4297,6 +4297,600 @@
         <v>223</v>
       </c>
       <c r="C55" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="C109" t="s" s="0">
         <v>198</v>
       </c>
     </row>
@@ -4307,7 +4901,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5113,6 +5707,1491 @@
         <v>198</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C140" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C142" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C144" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C145" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C146" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C147" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C148" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C149" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C150" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C151" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C152" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C153" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C154" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C155" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C156" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C157" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C158" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C159" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C160" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C161" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C162" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C163" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C164" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C165" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C166" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C167" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C168" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C169" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C170" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C171" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C172" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C173" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C174" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C175" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C177" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C178" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C180" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C181" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C182" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C183" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C184" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C186" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C187" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C188" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C189" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C190" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C192" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C193" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C194" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C195" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C196" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C197" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C198" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C199" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C200" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C201" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C202" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="C203" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C204" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C205" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C206" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C207" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C208" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497760\Ideaprojects\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497739\IdeaProjects\IdentifyNewBikes\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E008CE4-57D5-4C0C-A354-35351A46C240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C17B0B-E170-4C7E-B2E9-7C9BF4EAF7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BAA70594-9921-46EE-9B36-55EF6409868E}"/>
   </bookViews>

--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497739\IdeaProjects\IdentifyNewBikes\src\test\resources\"/>
     </mc:Choice>
@@ -14,10 +14,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HondaBikeDetails" r:id="rId5" sheetId="2"/>
+    <sheet name="BikesUnder4Lakhs" r:id="rId6" sheetId="3"/>
+    <sheet name="CarDetails" r:id="rId7" sheetId="4"/>
+    <sheet name="Under3LakhCars" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,8 +42,674 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="220">
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Expected Launch</t>
+  </si>
+  <si>
+    <t>Honda ADV 160</t>
+  </si>
+  <si>
+    <t>Rs. 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Dec 2026</t>
+  </si>
+  <si>
+    <t>Honda Shine Electric</t>
+  </si>
+  <si>
+    <t>Rs. 1.30 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Jan 2028</t>
+  </si>
+  <si>
+    <t>Honda CBR500R</t>
+  </si>
+  <si>
+    <t>Rs. 5.50 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Unrevealed</t>
+  </si>
+  <si>
+    <t>Honda Forza 350</t>
+  </si>
+  <si>
+    <t>Rs. 3.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 1100</t>
+  </si>
+  <si>
+    <t>Rs. 12.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB500F</t>
+  </si>
+  <si>
+    <t>Rs. 5.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CBR150R</t>
+  </si>
+  <si>
+    <t>Rs. 1.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 300</t>
+  </si>
+  <si>
+    <t>Rs. 2.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda PCX160</t>
+  </si>
+  <si>
+    <t>Rs. 1.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Motocompacto</t>
+  </si>
+  <si>
+    <t>Price To Be Announced</t>
+  </si>
+  <si>
+    <t>Honda CRF300L</t>
+  </si>
+  <si>
+    <t>Rs. 3.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB350 Cruiser</t>
+  </si>
+  <si>
+    <t>Honda Activa 7G</t>
+  </si>
+  <si>
+    <t>Rs. 79,000</t>
+  </si>
+  <si>
+    <t>Honda CB1000R</t>
+  </si>
+  <si>
+    <t>Rs. 14.46 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB1000GT</t>
+  </si>
+  <si>
+    <t>Honda WN7</t>
+  </si>
+  <si>
+    <t>Honda SH125i</t>
+  </si>
+  <si>
+    <t>Honda CL500 Scrambler</t>
+  </si>
+  <si>
+    <t>Rs. 6.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT</t>
+  </si>
+  <si>
+    <t>Rs. 6.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.75 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT SV</t>
+  </si>
+  <si>
+    <t>Rs. 5.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City SV MT</t>
+  </si>
+  <si>
+    <t>Rs. 5.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.35 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTec E</t>
+  </si>
+  <si>
+    <t>Rs. 5.85 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC E</t>
+  </si>
+  <si>
+    <t>Rs. 5.99 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC SV</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 4.66 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 3.75 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI</t>
+  </si>
+  <si>
+    <t>Rs. 3.80 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus AMT</t>
+  </si>
+  <si>
+    <t>Rs. 9.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT</t>
+  </si>
+  <si>
+    <t>Rs. 8.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX MT</t>
+  </si>
+  <si>
+    <t>Rs. 16.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.79 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX MT</t>
+  </si>
+  <si>
+    <t>Rs. 7.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City CVT</t>
+  </si>
+  <si>
+    <t>Rs. 17.60 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 7.49 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.96 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.12 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.40 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.16 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.83 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.75 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna</t>
+  </si>
+  <si>
+    <t>Rs. 3.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.06 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.17 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz</t>
+  </si>
+  <si>
+    <t>Rs. 2.10 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.70 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.1L</t>
+  </si>
+  <si>
+    <t>Rs. 3.65 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.45 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 5.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.84 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.95 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz AT</t>
+  </si>
+  <si>
+    <t>Rs. 2.70 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.10 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZDI</t>
+  </si>
+  <si>
+    <t>Rs. 4.94 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.30 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna 1.2</t>
+  </si>
+  <si>
+    <t>Rs. 2.25 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Asta</t>
+  </si>
+  <si>
+    <t>Rs. 2.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 13.00 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI BSIV</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT ZX</t>
+  </si>
+  <si>
+    <t>Rs. 3.59 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.25 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.30 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.0 G1</t>
+  </si>
+  <si>
+    <t>Rs. 5.90 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 9.90 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W11 AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 11.47 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 2.8 2WD AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 27.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.40 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS III</t>
+  </si>
+  <si>
+    <t>Rs. 3.15 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 EXI S</t>
+  </si>
+  <si>
+    <t>Rs. 2.65 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 2WD</t>
+  </si>
+  <si>
+    <t>Maruti Swift LDI</t>
+  </si>
+  <si>
+    <t>Rs. 2.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 8 Seater</t>
+  </si>
+  <si>
+    <t>Rs. 9.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 GXI</t>
+  </si>
+  <si>
+    <t>Rs. 1.60 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 26.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 15.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.75 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 9.00 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 4x4 AT</t>
+  </si>
+  <si>
+    <t>Rs. 22.00 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 2WD</t>
+  </si>
+  <si>
+    <t>Rs. 7.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.99 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT Exclusive</t>
+  </si>
+  <si>
+    <t>Rs. 5.30 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 12.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 15.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V AT</t>
+  </si>
+  <si>
+    <t>Honda City V</t>
+  </si>
+  <si>
+    <t>Rs. 10.17 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.40 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC ZX</t>
+  </si>
+  <si>
+    <t>Rs. 11.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT AVN</t>
+  </si>
+  <si>
+    <t>Rs. 4.35 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.45 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDi</t>
+  </si>
+  <si>
+    <t>Rs. 4.55 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing XO eRLX Euro II</t>
+  </si>
+  <si>
+    <t>Rs. 1.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VVT VXI</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.2 AT</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 R W10 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 10.50 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 AT W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 11.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.09 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.48 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S MT</t>
+  </si>
+  <si>
+    <t>Rs. 4.60 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.04 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 10.58 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX Plus</t>
+  </si>
+  <si>
+    <t>Rs. 11.59 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.13 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.44 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI Plus DT AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 7.82 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 5.55 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX Apex Edition CVT</t>
+  </si>
+  <si>
+    <t>Rs. 14.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.78 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 11.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.76 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.41 Lakh</t>
+  </si>
+  <si>
+    <t>Car Name</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,4 +1080,2859 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B258"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B245" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B246" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="B247" t="s" s="0">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B248" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B249" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B250" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B251" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B252" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="B253" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B254" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="B255" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B256" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B257" t="s" s="0">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B258" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497739\IdeaProjects\IdentifyNewBikes\src\test\resources\"/>
     </mc:Choice>
@@ -14,10 +14,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HondaBikeDetails" r:id="rId5" sheetId="2"/>
+    <sheet name="BikesUnder4Lakhs" r:id="rId6" sheetId="3"/>
+    <sheet name="CarDetails" r:id="rId7" sheetId="4"/>
+    <sheet name="Under3LakhCars" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,8 +42,674 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="220">
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Expected Launch</t>
+  </si>
+  <si>
+    <t>Honda ADV 160</t>
+  </si>
+  <si>
+    <t>Rs. 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Dec 2026</t>
+  </si>
+  <si>
+    <t>Honda Shine Electric</t>
+  </si>
+  <si>
+    <t>Rs. 1.30 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Jan 2028</t>
+  </si>
+  <si>
+    <t>Honda CBR500R</t>
+  </si>
+  <si>
+    <t>Rs. 5.50 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Unrevealed</t>
+  </si>
+  <si>
+    <t>Honda Forza 350</t>
+  </si>
+  <si>
+    <t>Rs. 3.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 1100</t>
+  </si>
+  <si>
+    <t>Rs. 12.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB500F</t>
+  </si>
+  <si>
+    <t>Rs. 5.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CBR150R</t>
+  </si>
+  <si>
+    <t>Rs. 1.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 300</t>
+  </si>
+  <si>
+    <t>Rs. 2.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda PCX160</t>
+  </si>
+  <si>
+    <t>Rs. 1.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Motocompacto</t>
+  </si>
+  <si>
+    <t>Price To Be Announced</t>
+  </si>
+  <si>
+    <t>Honda CRF300L</t>
+  </si>
+  <si>
+    <t>Rs. 3.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB350 Cruiser</t>
+  </si>
+  <si>
+    <t>Honda Activa 7G</t>
+  </si>
+  <si>
+    <t>Rs. 79,000</t>
+  </si>
+  <si>
+    <t>Honda CB1000R</t>
+  </si>
+  <si>
+    <t>Rs. 14.46 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB1000GT</t>
+  </si>
+  <si>
+    <t>Honda WN7</t>
+  </si>
+  <si>
+    <t>Honda SH125i</t>
+  </si>
+  <si>
+    <t>Honda CL500 Scrambler</t>
+  </si>
+  <si>
+    <t>Rs. 6.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT</t>
+  </si>
+  <si>
+    <t>Rs. 6.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.75 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT SV</t>
+  </si>
+  <si>
+    <t>Rs. 5.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City SV MT</t>
+  </si>
+  <si>
+    <t>Rs. 5.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.35 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC E</t>
+  </si>
+  <si>
+    <t>Rs. 5.99 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTec E</t>
+  </si>
+  <si>
+    <t>Rs. 5.85 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC SV</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.12 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.16 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.00 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI</t>
+  </si>
+  <si>
+    <t>Rs. 6.40 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna</t>
+  </si>
+  <si>
+    <t>Rs. 3.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.83 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.06 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.17 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.45 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S MT</t>
+  </si>
+  <si>
+    <t>Rs. 4.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT Exclusive</t>
+  </si>
+  <si>
+    <t>Rs. 4.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX MT</t>
+  </si>
+  <si>
+    <t>Rs. 10.04 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 10.58 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX Plus</t>
+  </si>
+  <si>
+    <t>Rs. 11.59 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.13 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI BSVI</t>
+  </si>
+  <si>
+    <t>Honda City VX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.44 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI Plus DT AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 7.82 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI BSIV</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 5.55 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX Apex Edition CVT</t>
+  </si>
+  <si>
+    <t>Rs. 14.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.78 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX MT</t>
+  </si>
+  <si>
+    <t>Rs. 9.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 11.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.30 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V</t>
+  </si>
+  <si>
+    <t>Rs. 9.41 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.96 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna 1.2</t>
+  </si>
+  <si>
+    <t>Rs. 2.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.30 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Asta</t>
+  </si>
+  <si>
+    <t>Rs. 2.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 13.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT ZX</t>
+  </si>
+  <si>
+    <t>Rs. 6.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.59 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.70 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz</t>
+  </si>
+  <si>
+    <t>Rs. 2.10 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.1L</t>
+  </si>
+  <si>
+    <t>Rs. 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.65 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.45 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.84 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.95 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz AT</t>
+  </si>
+  <si>
+    <t>Rs. 2.70 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.10 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 4.66 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZDI</t>
+  </si>
+  <si>
+    <t>Rs. 4.94 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 3.80 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus AMT</t>
+  </si>
+  <si>
+    <t>Rs. 9.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT</t>
+  </si>
+  <si>
+    <t>Rs. 8.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.79 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City CVT</t>
+  </si>
+  <si>
+    <t>Rs. 17.60 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 7.49 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.30 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.0 G1</t>
+  </si>
+  <si>
+    <t>Rs. 5.90 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 9.90 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W11 AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 11.47 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 2.8 2WD AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 27.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.40 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 EXI S</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS III</t>
+  </si>
+  <si>
+    <t>Rs. 3.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 2.65 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 2WD</t>
+  </si>
+  <si>
+    <t>Maruti Swift LDI</t>
+  </si>
+  <si>
+    <t>Rs. 2.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 8 Seater</t>
+  </si>
+  <si>
+    <t>Rs. 9.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 GXI</t>
+  </si>
+  <si>
+    <t>Rs. 1.60 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 26.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 15.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.75 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 9.00 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 4x4 AT</t>
+  </si>
+  <si>
+    <t>Rs. 22.00 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 2WD</t>
+  </si>
+  <si>
+    <t>Rs. 7.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.99 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 12.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 15.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V AT</t>
+  </si>
+  <si>
+    <t>Rs. 10.17 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.40 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC ZX</t>
+  </si>
+  <si>
+    <t>Rs. 11.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT AVN</t>
+  </si>
+  <si>
+    <t>Rs. 4.35 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.45 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDi</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing XO eRLX Euro II</t>
+  </si>
+  <si>
+    <t>Rs. 1.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VVT VXI</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.2 AT</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 R W10 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 10.50 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 AT W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 11.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.09 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.48 Lakh</t>
+  </si>
+  <si>
+    <t>Car Name</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,4 +1080,2955 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B270"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B245" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B246" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B247" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B248" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B249" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B250" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B251" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B252" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B253" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B254" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B255" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B256" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B257" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B258" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B259" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B260" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B261" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B262" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B263" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B264" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B265" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B266" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B267" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B268" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B269" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B270" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/Details.xlsx
+++ b/src/test/resources/Details.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497739\IdeaProjects\IdentifyNewBikes\src\test\resources\"/>
     </mc:Choice>
@@ -14,10 +14,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HondaBikeDetails" r:id="rId5" sheetId="2"/>
+    <sheet name="BikesUnder4Lakhs" r:id="rId6" sheetId="3"/>
+    <sheet name="CarDetails" r:id="rId7" sheetId="4"/>
+    <sheet name="Under3LakhCars" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,8 +42,674 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="220">
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Expected Launch</t>
+  </si>
+  <si>
+    <t>Honda ADV 160</t>
+  </si>
+  <si>
+    <t>Rs. 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Dec 2026</t>
+  </si>
+  <si>
+    <t>Honda Shine Electric</t>
+  </si>
+  <si>
+    <t>Rs. 1.30 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Jan 2028</t>
+  </si>
+  <si>
+    <t>Honda CBR500R</t>
+  </si>
+  <si>
+    <t>Rs. 5.50 Lakh</t>
+  </si>
+  <si>
+    <t>Expected Launch : Unrevealed</t>
+  </si>
+  <si>
+    <t>Honda Forza 350</t>
+  </si>
+  <si>
+    <t>Rs. 3.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 1100</t>
+  </si>
+  <si>
+    <t>Rs. 12.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB500F</t>
+  </si>
+  <si>
+    <t>Rs. 5.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CBR150R</t>
+  </si>
+  <si>
+    <t>Rs. 1.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Rebel 300</t>
+  </si>
+  <si>
+    <t>Rs. 2.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda PCX160</t>
+  </si>
+  <si>
+    <t>Rs. 1.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda Motocompacto</t>
+  </si>
+  <si>
+    <t>Price To Be Announced</t>
+  </si>
+  <si>
+    <t>Honda CRF300L</t>
+  </si>
+  <si>
+    <t>Rs. 3.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB350 Cruiser</t>
+  </si>
+  <si>
+    <t>Honda Activa 7G</t>
+  </si>
+  <si>
+    <t>Rs. 79,000</t>
+  </si>
+  <si>
+    <t>Honda CB1000R</t>
+  </si>
+  <si>
+    <t>Rs. 14.46 Lakh</t>
+  </si>
+  <si>
+    <t>Honda CB1000GT</t>
+  </si>
+  <si>
+    <t>Honda WN7</t>
+  </si>
+  <si>
+    <t>Honda SH125i</t>
+  </si>
+  <si>
+    <t>Honda CL500 Scrambler</t>
+  </si>
+  <si>
+    <t>Rs. 6.00 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI</t>
+  </si>
+  <si>
+    <t>Rs. 3.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT</t>
+  </si>
+  <si>
+    <t>Rs. 6.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.75 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT SV</t>
+  </si>
+  <si>
+    <t>Rs. 5.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City SV MT</t>
+  </si>
+  <si>
+    <t>Rs. 5.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.35 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC E</t>
+  </si>
+  <si>
+    <t>Rs. 5.99 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTec E</t>
+  </si>
+  <si>
+    <t>Rs. 5.85 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC SV</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.85 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.45 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S MT</t>
+  </si>
+  <si>
+    <t>Rs. 4.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT Exclusive</t>
+  </si>
+  <si>
+    <t>Rs. 4.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX MT</t>
+  </si>
+  <si>
+    <t>Rs. 10.04 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 10.58 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX Plus</t>
+  </si>
+  <si>
+    <t>Rs. 11.59 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.13 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.44 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI BSVI</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 5.55 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI Plus DT AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 7.82 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI BSIV</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI</t>
+  </si>
+  <si>
+    <t>Rs. 9.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX Apex Edition CVT</t>
+  </si>
+  <si>
+    <t>Rs. 14.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.78 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX MT</t>
+  </si>
+  <si>
+    <t>Rs. 9.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 11.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.76 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.30 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V</t>
+  </si>
+  <si>
+    <t>Rs. 9.41 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.12 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.16 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.40 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.83 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna</t>
+  </si>
+  <si>
+    <t>Rs. 3.20 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.06 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.17 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz</t>
+  </si>
+  <si>
+    <t>Rs. 2.10 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.1L</t>
+  </si>
+  <si>
+    <t>Rs. 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.65 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.70 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.84 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.95 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz AT</t>
+  </si>
+  <si>
+    <t>Rs. 2.70 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.10 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 4.66 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZDI</t>
+  </si>
+  <si>
+    <t>Rs. 4.94 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 3.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.80 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus AMT</t>
+  </si>
+  <si>
+    <t>Rs. 9.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT</t>
+  </si>
+  <si>
+    <t>Rs. 8.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.79 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.80 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City CVT</t>
+  </si>
+  <si>
+    <t>Rs. 17.60 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 7.49 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.96 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.30 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna 1.2</t>
+  </si>
+  <si>
+    <t>Rs. 2.25 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Asta</t>
+  </si>
+  <si>
+    <t>Rs. 2.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.20 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT ZX</t>
+  </si>
+  <si>
+    <t>Rs. 13.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.59 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.25 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.30 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.0 G1</t>
+  </si>
+  <si>
+    <t>Rs. 5.90 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 9.90 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W11 AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 11.47 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 2.8 2WD AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 27.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.40 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 EXI S</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS III</t>
+  </si>
+  <si>
+    <t>Rs. 3.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 2.65 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 2WD</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 8 Seater</t>
+  </si>
+  <si>
+    <t>Rs. 9.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 GXI</t>
+  </si>
+  <si>
+    <t>Rs. 1.60 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 26.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 15.90 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LDI</t>
+  </si>
+  <si>
+    <t>Rs. 2.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.75 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 9.00 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 4x4 AT</t>
+  </si>
+  <si>
+    <t>Rs. 22.00 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 2WD</t>
+  </si>
+  <si>
+    <t>Rs. 7.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.99 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 12.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 15.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V AT</t>
+  </si>
+  <si>
+    <t>Rs. 10.17 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.40 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC ZX</t>
+  </si>
+  <si>
+    <t>Rs. 11.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT AVN</t>
+  </si>
+  <si>
+    <t>Rs. 4.35 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.45 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDi</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing XO eRLX Euro II</t>
+  </si>
+  <si>
+    <t>Rs. 1.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VVT VXI</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.2 AT</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 R W10 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 10.50 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 AT W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 11.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.09 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.48 Lakh</t>
+  </si>
+  <si>
+    <t>Car Name</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,4 +1080,5975 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B516"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B245" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B246" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B247" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B248" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B249" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B250" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B251" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B252" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B253" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B254" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B255" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B256" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B257" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B258" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B259" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B260" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B261" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B262" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B263" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B264" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B265" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B266" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B267" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B268" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B269" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B270" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B271" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B272" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B273" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B274" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B275" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B276" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B277" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B278" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B279" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B280" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B281" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B282" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B283" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B284" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B285" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B286" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B287" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B288" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B289" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B290" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B291" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B292" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B293" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B294" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B295" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B296" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B297" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B298" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B299" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B300" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B301" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B302" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B303" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B304" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B305" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B306" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B307" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B308" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B309" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B310" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B311" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B312" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B313" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B314" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B315" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B316" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B317" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B318" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B319" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B320" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B321" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B322" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B323" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B324" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B325" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B326" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B327" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B328" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B329" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B330" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B331" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B332" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B333" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B334" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B335" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B336" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B337" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B338" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B339" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B340" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B341" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B342" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B343" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B344" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B345" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B346" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B347" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B348" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B349" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B350" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B351" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B352" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B353" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B354" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B355" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B356" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B357" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B358" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B359" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B360" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B361" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B362" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B363" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B364" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B365" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B366" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B367" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B368" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B369" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B370" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B371" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B372" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B373" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B374" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B375" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B376" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B377" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B378" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B379" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B380" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B381" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B382" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B383" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B384" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B385" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B386" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B387" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B388" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B389" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B390" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B391" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B392" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B393" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B394" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B395" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B396" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B397" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B398" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B399" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B400" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B401" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B402" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B403" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B404" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B405" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B406" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B407" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B408" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B409" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B410" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B411" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B412" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B413" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B414" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B415" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B416" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B417" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B418" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B419" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B420" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B421" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B422" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B423" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B424" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B425" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B426" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B427" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B428" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B429" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B430" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B431" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B432" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B433" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B434" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B435" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B436" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B437" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B438" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B439" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B440" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B441" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B442" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B443" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B444" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B445" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B446" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B447" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B448" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B449" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B450" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B451" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B452" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B453" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B454" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B455" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B456" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B457" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B458" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B459" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B460" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B461" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B462" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B463" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B464" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B465" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B466" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B467" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B468" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B469" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B470" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B471" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B472" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B473" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B474" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B475" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B476" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B477" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B478" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B479" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B480" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B481" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B482" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B483" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B484" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B485" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B486" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B487" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B488" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B489" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B490" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B491" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B492" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B493" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B494" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B495" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B496" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B497" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B498" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B499" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B500" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B501" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B502" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B503" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B504" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B505" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B506" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B507" t="s" s="0">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B508" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B509" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B510" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B511" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B512" t="s" s="0">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B513" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B514" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B515" t="s" s="0">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B516" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A79"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>